--- a/files/港岛-香港仔及鸭脷洲-璟南.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-璟南.xlsx
@@ -17,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="18">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -117,6 +119,11 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -194,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -206,6 +213,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -254,6 +264,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -630,8 +643,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -1655,23 +1668,19 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>56455300</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>33034</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -3403,100 +3412,100 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>璟南 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>38</t>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>31&amp;32</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 3523呎 (4+房)
 -
@@ -3504,15 +3513,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>29&amp;30</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 3518呎 (4+房)
 -
@@ -3520,15 +3529,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 2807呎 (4+房)
 -
@@ -3536,15 +3545,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 2807呎 (4+房)
 -
@@ -3552,15 +3561,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 2807呎 (4+房)
 -
@@ -3568,15 +3577,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 2792呎 (4+房)
 -
@@ -3584,15 +3593,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr"/>
+      <c r="C10" s="21" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 1709呎 (4+房)
 -
@@ -3600,7 +3609,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 1598呎 (4+房)
 -
@@ -3610,12 +3619,12 @@
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 1709呎 (4+房)
 -
@@ -3623,7 +3632,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 1598呎 (4+房)
 -
@@ -3633,12 +3642,12 @@
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 1709呎 (4+房)
 -
@@ -3646,7 +3655,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 1598呎 (4+房)
 -
@@ -3656,20 +3665,43 @@
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 1709呎 (4+房)
+$5646万
+$33,034/呎
+(26年-07月-31日)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1598呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1709呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 1598呎 (4+房)
 -
@@ -3678,13 +3710,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 1709呎 (4+房)
 -
@@ -3692,7 +3724,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 1598呎 (4+房)
 -
@@ -3701,13 +3733,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 1709呎 (4+房)
 -
@@ -3715,7 +3747,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 1598呎 (4+房)
 -
@@ -3724,13 +3756,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 1709呎 (4+房)
 -
@@ -3738,7 +3770,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 1598呎 (4+房)
 -
@@ -3747,13 +3779,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 1709呎 (4+房)
 -
@@ -3761,7 +3793,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 1598呎 (4+房)
 -
@@ -3770,13 +3802,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 1709呎 (4+房)
 -
@@ -3784,7 +3816,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 1598呎 (4+房)
 -
@@ -3793,13 +3825,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 1709呎 (4+房)
 -
@@ -3807,7 +3839,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 1598呎 (4+房)
 -
@@ -3816,13 +3848,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 1709呎 (4+房)
 -
@@ -3830,7 +3862,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 1598呎 (4+房)
 -
@@ -3839,13 +3871,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 1709呎 (4+房)
 -
@@ -3853,7 +3885,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 1598呎 (4+房)
 -
@@ -3862,13 +3894,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 1709呎 (4+房)
 -
@@ -3876,7 +3908,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 1598呎 (4+房)
 -
@@ -3885,13 +3917,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 1709呎 (4+房)
 -
@@ -3899,7 +3931,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 1598呎 (4+房)
 -
@@ -3908,13 +3940,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 1709呎 (4+房)
 -
@@ -3922,30 +3954,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 1598呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>A | 1709呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 1598呎 (4+房)
 -

--- a/files/港岛-香港仔及鸭脷洲-璟南.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-璟南.xlsx
@@ -1673,7 +1673,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -3675,7 +3675,7 @@
           <t>A | 1709呎 (4+房)
 $5646万
 $33,034/呎
-(26年-07月-31日)</t>
+(26年-08月-27日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
